--- a/InputData/indst/EoIEECwEC/Elasticity of Ind Eqpt E Cons wrt E Cost.xlsx
+++ b/InputData/indst/EoIEECwEC/Elasticity of Ind Eqpt E Cons wrt E Cost.xlsx
@@ -1,146 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\EoIEECwEC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB3AF3A-6B28-45CB-9AA4-A910A7506878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-26220" yWindow="1965" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-26220" yWindow="1965" windowWidth="21600" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="EoIEECwEC" sheetId="3" r:id="rId2"/>
+    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EoIEECwEC" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>EoIEECwEC Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable represents the elasticity of industrial equipment's energy consumption (per unit industrial output)</t>
-  </si>
-  <si>
-    <t>in the energy efficiency of the equipment, not changes in how much the equipment is run.</t>
-  </si>
-  <si>
-    <t>(Changes in how much the equipment is run are already handled elsewhere in the model, where production</t>
-  </si>
-  <si>
-    <t>is scaled up or down based on energy costs and other factors.)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">with respect to the price of the energy used by that equipment.  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>In other words, it reflects technical improvements</t>
-    </r>
-  </si>
-  <si>
-    <t>This variable applies to newly sold equipment, not existing equipment.  Therefore, we use</t>
-  </si>
-  <si>
-    <t>long-run elasticities from economic studies, which reflect the change in energy use after equipment</t>
-  </si>
-  <si>
-    <t>minimizing the contribution of behavioral change to the elasticity.)</t>
-  </si>
-  <si>
-    <t>has had time to turn over. (Also, "long run" gives people time to habituate to new pricing levels,</t>
-  </si>
-  <si>
-    <t>Elasticity</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
-  </si>
-  <si>
-    <t>Energy Prices and the Adoption of Energy-Saving Technology</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/doi/abs/10.1111/j.1468-0297.2008.02199.x</t>
-  </si>
-  <si>
-    <t>Table 2</t>
-  </si>
-  <si>
-    <t>elasticity</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -165,32 +69,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -510,126 +473,281 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F6B216-0153-49F1-A327-FA35702ED267}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="60.42578125" customWidth="1"/>
+    <col width="60.42578125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EoIEECwEC Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source:</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Elasticity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Linn, Joshua (2008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Energy Prices and the Adoption of Energy-Saving Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/abs/10.1111/j.1468-0297.2008.02199.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Location in source</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Economic Journal 118(533): 1986-2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>This variable represents the elasticity of industrial equipment's energy consumption (per unit industrial output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>with respect to the price of the energy used by that equipment.  In other words, it reflects technical improvements</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>in the energy efficiency of the equipment, not changes in how much the equipment is run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(Changes in how much the equipment is run are already handled elsewhere in the model, where production</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>is scaled up or down based on energy costs and other factors.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>This variable applies to newly sold equipment, not existing equipment.  Therefore, we use</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>long-run elasticities from economic studies, which reflect the change in energy use after equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>has had time to turn over. (Also, "long run" gives people time to habituate to new pricing levels,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>minimizing the contribution of behavioral change to the elasticity.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>The value -0.1 is the headline technology-adoption estimate (delta-1 = -0.100, SE 0.026) from Table 2, column 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Linn characterizes it as a lower bound on the adoption response. Robustness range across specifications: -0.045 to -0.122.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>On sector disaggregation (reviewed 2026-08-12): Steinbuks &amp; Neuhoff (2014), Assessing energy price induced improvements</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>in efficiency of capital in OECD manufacturing industries, JEEM 68(2): 340-356 (WB PRWP 6929), Table 3, estimate the</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>elasticity of energy input efficiency of new capital wrt energy prices by sector: petrochemical 1.10 (SE 0.13), metals 1.08 (0.12),</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>food processing 0.50 (0.12), electrical/optical 0.02 (0.08, insignificant), pulp &amp; paper 0.02 (0.27, insignificant - the paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>attributes this to low investment volumes 1990-2005, not true unresponsiveness). We keep a uniform -0.1 because: only 5 coarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sectors map poorly to EPS Industry Categories; 2 of 5 estimates are statistically zero (one self-acknowledged as artifactual);</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>estimates come from a structural vintage-capital model, not quasi-experimental variation like Linn; and the S&amp;N levels (0.5-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>where significant) are 5-11x Linn, so mixing the two sources would be internally inconsistent. Net: -0.1 is conservative,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>especially for energy-intensive sectors. Revisit only with a source offering both finer sector resolution and consistent levels.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB977EF-DFFE-4EEF-A0E1-DBBDDDFA9996}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="3" tint="9.9978637043366805E-2"/>
+    <tabColor theme="3" tint="0.09997863704336681"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col width="33.5703125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Unit: dimensionless</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>elasticity</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>-0.1</v>
       </c>
     </row>
